--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.69829569423521</v>
+        <v>4.338473050313223</v>
       </c>
       <c r="D2" t="n">
-        <v>26.61333460986057</v>
+        <v>4.324666874102343</v>
       </c>
       <c r="E2" t="n">
-        <v>12.33276524614127</v>
+        <v>2.004074352497957</v>
       </c>
       <c r="F2" t="n">
-        <v>8.935382704563654</v>
+        <v>1.451999689491594</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.83797955062386</v>
+        <v>9.073671676976378</v>
       </c>
       <c r="D3" t="n">
-        <v>11.66417333835438</v>
+        <v>1.895428167482586</v>
       </c>
       <c r="E3" t="n">
-        <v>12.33276524614127</v>
+        <v>2.004074352497957</v>
       </c>
       <c r="F3" t="n">
-        <v>8.935382704563654</v>
+        <v>1.451999689491594</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.16712757286628</v>
+        <v>7.827158230590771</v>
       </c>
       <c r="D4" t="n">
-        <v>5.294017743126287</v>
+        <v>0.8602778832580217</v>
       </c>
       <c r="E4" t="n">
-        <v>12.33276524614127</v>
+        <v>2.004074352497957</v>
       </c>
       <c r="F4" t="n">
-        <v>8.935382704563654</v>
+        <v>1.451999689491594</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
